--- a/Result/profitability/2354.xlsx
+++ b/Result/profitability/2354.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.64</v>
       </c>
       <c r="M2" t="n">
-        <v>0.71875</v>
+        <v>0.71125</v>
       </c>
       <c r="N2" t="n">
-        <v>4.7575</v>
+        <v>4.43</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.19</v>
       </c>
       <c r="M3" t="n">
-        <v>0.78125</v>
+        <v>0.78</v>
       </c>
       <c r="N3" t="n">
-        <v>5.01625</v>
+        <v>5.0175</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>2.85</v>
       </c>
       <c r="M4" t="n">
-        <v>1.0575</v>
+        <v>1.0525</v>
       </c>
       <c r="N4" t="n">
-        <v>5.80625</v>
+        <v>5.7725</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>1.81</v>
       </c>
       <c r="M5" t="n">
-        <v>1.2</v>
+        <v>1.23125</v>
       </c>
       <c r="N5" t="n">
-        <v>6.155</v>
+        <v>6.287500000000001</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>1.07</v>
       </c>
       <c r="M6" t="n">
-        <v>1.28625</v>
+        <v>1.2875</v>
       </c>
       <c r="N6" t="n">
-        <v>6.3775</v>
+        <v>6.42875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.91</v>
       </c>
       <c r="M7" t="n">
-        <v>1.3225</v>
+        <v>1.32125</v>
       </c>
       <c r="N7" t="n">
-        <v>7.14</v>
+        <v>7.11625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>2.04</v>
       </c>
       <c r="M8" t="n">
-        <v>1.4975</v>
+        <v>1.5175</v>
       </c>
       <c r="N8" t="n">
-        <v>7.84</v>
+        <v>7.73875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2354</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>30341</v>
+      </c>
+      <c r="D75" t="n">
+        <v>29118</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1223</v>
+      </c>
+      <c r="F75" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="G75" t="n">
+        <v>343</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>1.13%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>1031</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1374</v>
+      </c>
+      <c r="K75" t="n">
+        <v>890</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.5925</v>
+      </c>
+      <c r="N75" t="n">
+        <v>4.33125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.3404255319148937</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.8099999999999996</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1673553719008264</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.6578947368421053</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.3569023569023568</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
